--- a/assets/plantilla-importacion-indicadores.xlsx
+++ b/assets/plantilla-importacion-indicadores.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -425,79 +425,89 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1. Llene solo las hojas que necesite. Las filas de ejemplo puede borrarlas o sustituirlas.</v>
+        <v>1. Llene solo las celdas que corresponden a datos ya ocurridos. Filas futuras pueden dejarse en blanco.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. clave_mes debe ser YYYY-MM (ej. 2026-04).</v>
+        <v>2. Esta plantilla se genera con el mes de referencia: año 2026, mes 4 (2026-04).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3. En hojas *_detalle, tipo = semana (semana ISO) o dia (día del mes 1-31).</v>
+        <v xml:space="preserve">   Para otro mes, ejecute: TEMPLATE_YEAR=2026 TEMPLATE_MONTH=5 npm run build:template</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4. periodo = número de semana ISO (1-53) o día del mes según el tipo.</v>
+        <v>3. clave_mes debe ser YYYY-MM (ej. 2026-04). En *_detalle del mes actual ya viene rellenada.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>5. Importe desde la página Captura (archivo .xlsx o .xls). Los datos se fusionan con lo ya guardado.</v>
+        <v>4. En hojas *_detalle, tipo = semana (número de semana ISO) o dia (día del mes 1-30).</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>5. periodo = semana ISO (1-53) o día del mes según el tipo.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Hojas</v>
+        <v>6. Importe desde la página Captura. Los datos se fusionan con lo ya guardado en el navegador.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>carros_uct_anual — Promedio UCT por mes del año</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>carros_total_mes — Total UCT del mes (campo mensual del mes)</v>
+        <v>Hojas</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>carros_detalle — Desglose por categoría (Carros Taller)</v>
+        <v>carros_uct_anual — UCT promedio por mes (12 meses del año 2026)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>semaforo_anual / semaforo_detalle — Semáforo de llantas</v>
+        <v>carros_total_mes — Total UCT del mes (una fila por mes del año)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>flota360_anual / flota360_detalle — Evaluación Flota 360</v>
+        <v>carros_detalle — Semanas ISO que caen en 2026-04 + un día por fila (1-30)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>semaforo_anual / semaforo_detalle — Semáforo de llantas</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>flota360_anual / flota360_detalle — Evaluación Flota 360</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>mtto_anual / mtto_detalle — MTTO preventivo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -538,28 +548,589 @@
         <v>2026-04</v>
       </c>
       <c r="B3" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B4" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B6" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B7" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B8" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B9" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B10" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B11" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B12" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B13" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B14" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B15" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C15">
         <v>9</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B16" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B17" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B18" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B19" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C19">
+        <v>13</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B20" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B21" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B22" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B23" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C23">
+        <v>17</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B24" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C24">
+        <v>18</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B25" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C25">
+        <v>19</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B26" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B27" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C27">
+        <v>21</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C28">
+        <v>22</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B29" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C29">
+        <v>23</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B30" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C30">
+        <v>24</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B31" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C31">
+        <v>25</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B32" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C32">
+        <v>26</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B33" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C33">
+        <v>27</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B34" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C34">
+        <v>28</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B35" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C35">
+        <v>29</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B36" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C36">
+        <v>30</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -616,16 +1187,104 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2026</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -637,22 +1296,110 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-01</v>
       </c>
       <c r="B2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-09</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-12</v>
+      </c>
+      <c r="B13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -711,37 +1458,895 @@
         <v>2026-04</v>
       </c>
       <c r="B3" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B4" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B6" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B7" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B8" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B9" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B10" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B11" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B12" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B13" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B14" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B15" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B16" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B17" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B18" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B19" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C19">
+        <v>13</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B20" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B21" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B22" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B23" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C23">
+        <v>17</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B24" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C24">
+        <v>18</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B25" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C25">
+        <v>19</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B26" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B27" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C27">
+        <v>21</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C28">
+        <v>22</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B29" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C29">
+        <v>23</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B30" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C30">
+        <v>24</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B31" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C31">
+        <v>25</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B32" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C32">
+        <v>26</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B33" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C33">
+        <v>27</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B34" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C34">
+        <v>28</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B35" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C35">
+        <v>29</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B36" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C36">
+        <v>30</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -762,25 +2367,179 @@
         <v>2026</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2026</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -821,28 +2580,589 @@
         <v>2026-04</v>
       </c>
       <c r="B3" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B4" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B6" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B7" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B8" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B9" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B10" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B11" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B12" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B13" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B14" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B15" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C15">
         <v>9</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B16" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B17" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B18" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B19" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C19">
+        <v>13</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B20" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B21" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B22" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B23" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C23">
+        <v>17</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B24" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C24">
+        <v>18</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B25" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C25">
+        <v>19</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B26" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B27" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C27">
+        <v>21</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C28">
+        <v>22</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B29" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C29">
+        <v>23</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B30" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C30">
+        <v>24</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B31" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C31">
+        <v>25</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B32" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C32">
+        <v>26</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B33" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C33">
+        <v>27</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B34" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C34">
+        <v>28</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B35" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C35">
+        <v>29</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B36" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C36">
+        <v>30</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -863,25 +3183,179 @@
         <v>2026</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2026</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -922,28 +3396,589 @@
         <v>2026-04</v>
       </c>
       <c r="B3" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B4" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B6" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B7" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B8" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B9" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B10" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B11" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B12" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B13" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B14" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B15" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C15">
         <v>9</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B16" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B17" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B18" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B19" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C19">
+        <v>13</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B20" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B21" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B22" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B23" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C23">
+        <v>17</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B24" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C24">
+        <v>18</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B25" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C25">
+        <v>19</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B26" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B27" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C27">
+        <v>21</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C28">
+        <v>22</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B29" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C29">
+        <v>23</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B30" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C30">
+        <v>24</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B31" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C31">
+        <v>25</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B32" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C32">
+        <v>26</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B33" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C33">
+        <v>27</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B34" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C34">
+        <v>28</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B35" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C35">
+        <v>29</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B36" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C36">
+        <v>30</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -964,18 +3999,172 @@
         <v>2026</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2026</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/plantilla-importacion-indicadores.xlsx
+++ b/assets/plantilla-importacion-indicadores.xlsx
@@ -430,7 +430,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. Esta plantilla se genera con el mes de referencia: año 2026, mes 4 (2026-04).</v>
+        <v>2. Esta plantilla se genera con el mes de referencia: año 2026, mes 5 (2026-05).</v>
       </c>
     </row>
     <row r="6">
@@ -445,7 +445,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>4. En hojas *_detalle, tipo = semana (número de semana ISO) o dia (día del mes 1-30).</v>
+        <v>4. En hojas *_detalle, tipo = semana (número de semana ISO) o dia (día del mes 1-31).</v>
       </c>
     </row>
     <row r="9">
@@ -480,7 +480,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>carros_detalle — Semanas ISO que caen en 2026-04 + un día por fila (1-30)</v>
+        <v>carros_detalle — Semanas ISO que caen en 2026-05 + un día por fila (1-31)</v>
       </c>
     </row>
     <row r="16">
@@ -507,7 +507,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -528,13 +528,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -545,13 +545,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -562,13 +562,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -579,13 +579,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -596,13 +596,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -613,7 +613,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B7" t="str">
         <v>dia</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B8" t="str">
         <v>dia</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B9" t="str">
         <v>dia</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B10" t="str">
         <v>dia</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B11" t="str">
         <v>dia</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B12" t="str">
         <v>dia</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B13" t="str">
         <v>dia</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B14" t="str">
         <v>dia</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B15" t="str">
         <v>dia</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B16" t="str">
         <v>dia</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B17" t="str">
         <v>dia</v>
@@ -800,7 +800,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B18" t="str">
         <v>dia</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B19" t="str">
         <v>dia</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B20" t="str">
         <v>dia</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B21" t="str">
         <v>dia</v>
@@ -868,7 +868,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B22" t="str">
         <v>dia</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B23" t="str">
         <v>dia</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B24" t="str">
         <v>dia</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B25" t="str">
         <v>dia</v>
@@ -936,7 +936,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B26" t="str">
         <v>dia</v>
@@ -953,7 +953,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B27" t="str">
         <v>dia</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B28" t="str">
         <v>dia</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B29" t="str">
         <v>dia</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B30" t="str">
         <v>dia</v>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B31" t="str">
         <v>dia</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B32" t="str">
         <v>dia</v>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B33" t="str">
         <v>dia</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B34" t="str">
         <v>dia</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B35" t="str">
         <v>dia</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B36" t="str">
         <v>dia</v>
@@ -1121,9 +1121,26 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B37" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C37">
+        <v>31</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1399,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1429,13 +1446,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -1455,13 +1472,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -1481,13 +1498,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -1507,13 +1524,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -1533,13 +1550,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -1559,7 +1576,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B7" t="str">
         <v>dia</v>
@@ -1585,7 +1602,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B8" t="str">
         <v>dia</v>
@@ -1611,7 +1628,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B9" t="str">
         <v>dia</v>
@@ -1637,7 +1654,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B10" t="str">
         <v>dia</v>
@@ -1663,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B11" t="str">
         <v>dia</v>
@@ -1689,7 +1706,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B12" t="str">
         <v>dia</v>
@@ -1715,7 +1732,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B13" t="str">
         <v>dia</v>
@@ -1741,7 +1758,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B14" t="str">
         <v>dia</v>
@@ -1767,7 +1784,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B15" t="str">
         <v>dia</v>
@@ -1793,7 +1810,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B16" t="str">
         <v>dia</v>
@@ -1819,7 +1836,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B17" t="str">
         <v>dia</v>
@@ -1845,7 +1862,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B18" t="str">
         <v>dia</v>
@@ -1871,7 +1888,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B19" t="str">
         <v>dia</v>
@@ -1897,7 +1914,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B20" t="str">
         <v>dia</v>
@@ -1923,7 +1940,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B21" t="str">
         <v>dia</v>
@@ -1949,7 +1966,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B22" t="str">
         <v>dia</v>
@@ -1975,7 +1992,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B23" t="str">
         <v>dia</v>
@@ -2001,7 +2018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B24" t="str">
         <v>dia</v>
@@ -2027,7 +2044,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B25" t="str">
         <v>dia</v>
@@ -2053,7 +2070,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B26" t="str">
         <v>dia</v>
@@ -2079,7 +2096,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B27" t="str">
         <v>dia</v>
@@ -2105,7 +2122,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B28" t="str">
         <v>dia</v>
@@ -2131,7 +2148,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B29" t="str">
         <v>dia</v>
@@ -2157,7 +2174,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B30" t="str">
         <v>dia</v>
@@ -2183,7 +2200,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B31" t="str">
         <v>dia</v>
@@ -2209,7 +2226,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B32" t="str">
         <v>dia</v>
@@ -2235,7 +2252,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B33" t="str">
         <v>dia</v>
@@ -2261,7 +2278,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B34" t="str">
         <v>dia</v>
@@ -2287,7 +2304,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B35" t="str">
         <v>dia</v>
@@ -2313,7 +2330,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B36" t="str">
         <v>dia</v>
@@ -2337,9 +2354,35 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B37" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C37">
+        <v>31</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2539,7 +2582,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2560,13 +2603,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -2577,13 +2620,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -2594,13 +2637,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -2611,13 +2654,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -2628,13 +2671,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -2645,7 +2688,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B7" t="str">
         <v>dia</v>
@@ -2662,7 +2705,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B8" t="str">
         <v>dia</v>
@@ -2679,7 +2722,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B9" t="str">
         <v>dia</v>
@@ -2696,7 +2739,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B10" t="str">
         <v>dia</v>
@@ -2713,7 +2756,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B11" t="str">
         <v>dia</v>
@@ -2730,7 +2773,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B12" t="str">
         <v>dia</v>
@@ -2747,7 +2790,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B13" t="str">
         <v>dia</v>
@@ -2764,7 +2807,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B14" t="str">
         <v>dia</v>
@@ -2781,7 +2824,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B15" t="str">
         <v>dia</v>
@@ -2798,7 +2841,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B16" t="str">
         <v>dia</v>
@@ -2815,7 +2858,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B17" t="str">
         <v>dia</v>
@@ -2832,7 +2875,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B18" t="str">
         <v>dia</v>
@@ -2849,7 +2892,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B19" t="str">
         <v>dia</v>
@@ -2866,7 +2909,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B20" t="str">
         <v>dia</v>
@@ -2883,7 +2926,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B21" t="str">
         <v>dia</v>
@@ -2900,7 +2943,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B22" t="str">
         <v>dia</v>
@@ -2917,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B23" t="str">
         <v>dia</v>
@@ -2934,7 +2977,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B24" t="str">
         <v>dia</v>
@@ -2951,7 +2994,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B25" t="str">
         <v>dia</v>
@@ -2968,7 +3011,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B26" t="str">
         <v>dia</v>
@@ -2985,7 +3028,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B27" t="str">
         <v>dia</v>
@@ -3002,7 +3045,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B28" t="str">
         <v>dia</v>
@@ -3019,7 +3062,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B29" t="str">
         <v>dia</v>
@@ -3036,7 +3079,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B30" t="str">
         <v>dia</v>
@@ -3053,7 +3096,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B31" t="str">
         <v>dia</v>
@@ -3070,7 +3113,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B32" t="str">
         <v>dia</v>
@@ -3087,7 +3130,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B33" t="str">
         <v>dia</v>
@@ -3104,7 +3147,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B34" t="str">
         <v>dia</v>
@@ -3121,7 +3164,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B35" t="str">
         <v>dia</v>
@@ -3138,7 +3181,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B36" t="str">
         <v>dia</v>
@@ -3153,9 +3196,26 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B37" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C37">
+        <v>31</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3355,7 +3415,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3376,13 +3436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -3393,13 +3453,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -3410,13 +3470,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -3427,13 +3487,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -3444,13 +3504,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -3461,7 +3521,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B7" t="str">
         <v>dia</v>
@@ -3478,7 +3538,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B8" t="str">
         <v>dia</v>
@@ -3495,7 +3555,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B9" t="str">
         <v>dia</v>
@@ -3512,7 +3572,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B10" t="str">
         <v>dia</v>
@@ -3529,7 +3589,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B11" t="str">
         <v>dia</v>
@@ -3546,7 +3606,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B12" t="str">
         <v>dia</v>
@@ -3563,7 +3623,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B13" t="str">
         <v>dia</v>
@@ -3580,7 +3640,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B14" t="str">
         <v>dia</v>
@@ -3597,7 +3657,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B15" t="str">
         <v>dia</v>
@@ -3614,7 +3674,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B16" t="str">
         <v>dia</v>
@@ -3631,7 +3691,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B17" t="str">
         <v>dia</v>
@@ -3648,7 +3708,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B18" t="str">
         <v>dia</v>
@@ -3665,7 +3725,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B19" t="str">
         <v>dia</v>
@@ -3682,7 +3742,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B20" t="str">
         <v>dia</v>
@@ -3699,7 +3759,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B21" t="str">
         <v>dia</v>
@@ -3716,7 +3776,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B22" t="str">
         <v>dia</v>
@@ -3733,7 +3793,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B23" t="str">
         <v>dia</v>
@@ -3750,7 +3810,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B24" t="str">
         <v>dia</v>
@@ -3767,7 +3827,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B25" t="str">
         <v>dia</v>
@@ -3784,7 +3844,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B26" t="str">
         <v>dia</v>
@@ -3801,7 +3861,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B27" t="str">
         <v>dia</v>
@@ -3818,7 +3878,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B28" t="str">
         <v>dia</v>
@@ -3835,7 +3895,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B29" t="str">
         <v>dia</v>
@@ -3852,7 +3912,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B30" t="str">
         <v>dia</v>
@@ -3869,7 +3929,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B31" t="str">
         <v>dia</v>
@@ -3886,7 +3946,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B32" t="str">
         <v>dia</v>
@@ -3903,7 +3963,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B33" t="str">
         <v>dia</v>
@@ -3920,7 +3980,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B34" t="str">
         <v>dia</v>
@@ -3937,7 +3997,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B35" t="str">
         <v>dia</v>
@@ -3954,7 +4014,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B36" t="str">
         <v>dia</v>
@@ -3969,9 +4029,26 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B37" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C37">
+        <v>31</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/assets/plantilla-importacion-indicadores.xlsx
+++ b/assets/plantilla-importacion-indicadores.xlsx
@@ -430,7 +430,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. Esta plantilla se genera con el mes de referencia: año 2026, mes 5 (2026-05).</v>
+        <v>2. Esta plantilla se genera con el mes de referencia: año 2026, mes 4 (2026-04).</v>
       </c>
     </row>
     <row r="6">
@@ -445,7 +445,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>4. En hojas *_detalle, tipo = semana (número de semana ISO) o dia (día del mes 1-31).</v>
+        <v>4. En *_detalle: filas semana = semanas ISO 1-53 (como en pantalla Captura); luego filas dia = días 1-30 del mes.</v>
       </c>
     </row>
     <row r="9">
@@ -480,7 +480,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>carros_detalle — Semanas ISO que caen en 2026-05 + un día por fila (1-31)</v>
+        <v>carros_detalle — Semanas ISO 1-53 + un día por fila del mes (1-30), clave_mes 2026-04</v>
       </c>
     </row>
     <row r="16">
@@ -507,7 +507,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E84"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -528,13 +528,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -545,13 +545,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -562,13 +562,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -579,13 +579,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -596,13 +596,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -613,13 +613,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B7" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -630,13 +630,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B8" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -647,13 +647,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B9" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -664,13 +664,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B10" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -681,13 +681,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B11" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -698,13 +698,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B12" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -715,13 +715,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B13" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -732,13 +732,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B14" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -749,13 +749,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B15" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -766,13 +766,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B16" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -783,13 +783,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B17" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -800,13 +800,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B18" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -817,13 +817,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B19" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -834,13 +834,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B20" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -851,13 +851,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B21" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -868,13 +868,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B22" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -885,13 +885,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B23" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -902,13 +902,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B24" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C24">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B25" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -936,13 +936,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B26" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -953,13 +953,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B27" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -970,13 +970,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B28" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -987,13 +987,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B29" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -1004,13 +1004,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B30" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C30">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1021,13 +1021,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B31" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1038,13 +1038,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B32" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -1055,13 +1055,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B33" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C33">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1072,13 +1072,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B34" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C34">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -1089,13 +1089,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B35" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C35">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -1106,13 +1106,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B36" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -1123,24 +1123,823 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B37" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C37">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B38" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C38">
+        <v>37</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B39" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B40" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C40">
+        <v>39</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B41" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B42" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B43" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C43">
+        <v>42</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B44" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B45" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C45">
+        <v>44</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B46" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B47" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C47">
+        <v>46</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B48" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C48">
+        <v>47</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B49" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C49">
+        <v>48</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B50" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C50">
+        <v>49</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B51" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B52" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C52">
+        <v>51</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B53" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C53">
+        <v>52</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B54" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C54">
+        <v>53</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B55" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B56" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B57" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B58" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B59" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B60" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C60">
+        <v>6</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B61" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B62" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B63" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C63">
+        <v>9</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B64" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B65" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C65">
+        <v>11</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B66" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C66">
+        <v>12</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B67" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C67">
+        <v>13</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B68" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C68">
+        <v>14</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B69" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C69">
+        <v>15</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B70" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C70">
+        <v>16</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B71" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C71">
+        <v>17</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B72" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C72">
+        <v>18</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B73" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C73">
+        <v>19</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B74" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C74">
+        <v>20</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B75" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C75">
+        <v>21</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B76" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C76">
+        <v>22</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B77" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C77">
+        <v>23</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B78" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C78">
+        <v>24</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B79" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C79">
+        <v>25</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B80" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C80">
+        <v>26</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B81" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C81">
+        <v>27</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B82" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C82">
+        <v>28</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B83" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C83">
+        <v>29</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B84" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C84">
+        <v>30</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E84"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1416,7 +2215,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H84"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1446,13 +2245,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -1472,13 +2271,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -1498,13 +2297,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -1524,13 +2323,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -1550,13 +2349,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -1576,13 +2375,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B7" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -1602,13 +2401,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B8" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -1628,13 +2427,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B9" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -1654,13 +2453,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B10" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -1680,13 +2479,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B11" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -1706,13 +2505,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B12" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -1732,13 +2531,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B13" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -1758,13 +2557,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B14" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -1784,13 +2583,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B15" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -1810,13 +2609,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B16" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -1836,13 +2635,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B17" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -1862,13 +2661,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B18" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -1888,13 +2687,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B19" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -1914,13 +2713,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B20" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -1940,13 +2739,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B21" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -1966,13 +2765,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B22" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -1992,13 +2791,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B23" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -2018,13 +2817,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B24" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C24">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -2044,13 +2843,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B25" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -2070,13 +2869,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B26" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -2096,13 +2895,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B27" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -2122,13 +2921,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B28" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -2148,13 +2947,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B29" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -2174,13 +2973,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B30" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C30">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -2200,13 +2999,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B31" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -2226,13 +3025,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B32" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -2252,13 +3051,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B33" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C33">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -2278,13 +3077,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B34" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C34">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -2304,13 +3103,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B35" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C35">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -2330,13 +3129,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B36" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -2356,13 +3155,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B37" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C37">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -2377,12 +3176,1234 @@
         <v/>
       </c>
       <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B38" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C38">
+        <v>37</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B39" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B40" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C40">
+        <v>39</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B41" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B42" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B43" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C43">
+        <v>42</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B44" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B45" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C45">
+        <v>44</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B46" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B47" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C47">
+        <v>46</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B48" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C48">
+        <v>47</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B49" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C49">
+        <v>48</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B50" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C50">
+        <v>49</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B51" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B52" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C52">
+        <v>51</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B53" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C53">
+        <v>52</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B54" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C54">
+        <v>53</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B55" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B56" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B57" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B58" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B59" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B60" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C60">
+        <v>6</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B61" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B62" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B63" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C63">
+        <v>9</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B64" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B65" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C65">
+        <v>11</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B66" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C66">
+        <v>12</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B67" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C67">
+        <v>13</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B68" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C68">
+        <v>14</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B69" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C69">
+        <v>15</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B70" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C70">
+        <v>16</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B71" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C71">
+        <v>17</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B72" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C72">
+        <v>18</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B73" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C73">
+        <v>19</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B74" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C74">
+        <v>20</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B75" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C75">
+        <v>21</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B76" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C76">
+        <v>22</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B77" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C77">
+        <v>23</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B78" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C78">
+        <v>24</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B79" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C79">
+        <v>25</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B80" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C80">
+        <v>26</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B81" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C81">
+        <v>27</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B82" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C82">
+        <v>28</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B83" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C83">
+        <v>29</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B84" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C84">
+        <v>30</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H84"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2582,7 +4603,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E84"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2603,13 +4624,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -2620,13 +4641,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -2637,13 +4658,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -2654,13 +4675,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -2671,13 +4692,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -2688,13 +4709,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B7" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -2705,13 +4726,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B8" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -2722,13 +4743,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B9" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -2739,13 +4760,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B10" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -2756,13 +4777,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B11" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -2773,13 +4794,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B12" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -2790,13 +4811,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B13" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -2807,13 +4828,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B14" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -2824,13 +4845,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B15" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -2841,13 +4862,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B16" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -2858,13 +4879,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B17" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -2875,13 +4896,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B18" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -2892,13 +4913,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B19" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -2909,13 +4930,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B20" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -2926,13 +4947,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B21" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -2943,13 +4964,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B22" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -2960,13 +4981,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B23" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -2977,13 +4998,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B24" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C24">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -2994,13 +5015,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B25" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -3011,13 +5032,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B26" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -3028,13 +5049,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B27" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -3045,13 +5066,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B28" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -3062,13 +5083,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B29" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -3079,13 +5100,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B30" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C30">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -3096,13 +5117,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B31" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -3113,13 +5134,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B32" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -3130,13 +5151,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B33" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C33">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -3147,13 +5168,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B34" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C34">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -3164,13 +5185,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B35" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C35">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -3181,13 +5202,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B36" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -3198,24 +5219,823 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B37" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C37">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B38" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C38">
+        <v>37</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B39" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B40" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C40">
+        <v>39</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B41" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B42" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B43" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C43">
+        <v>42</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B44" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B45" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C45">
+        <v>44</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B46" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B47" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C47">
+        <v>46</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B48" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C48">
+        <v>47</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B49" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C49">
+        <v>48</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B50" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C50">
+        <v>49</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B51" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B52" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C52">
+        <v>51</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B53" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C53">
+        <v>52</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B54" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C54">
+        <v>53</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B55" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B56" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B57" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B58" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B59" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B60" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C60">
+        <v>6</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B61" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B62" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B63" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C63">
+        <v>9</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B64" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B65" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C65">
+        <v>11</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B66" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C66">
+        <v>12</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B67" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C67">
+        <v>13</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B68" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C68">
+        <v>14</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B69" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C69">
+        <v>15</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B70" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C70">
+        <v>16</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B71" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C71">
+        <v>17</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B72" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C72">
+        <v>18</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B73" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C73">
+        <v>19</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B74" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C74">
+        <v>20</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B75" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C75">
+        <v>21</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B76" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C76">
+        <v>22</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B77" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C77">
+        <v>23</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B78" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C78">
+        <v>24</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B79" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C79">
+        <v>25</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B80" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C80">
+        <v>26</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B81" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C81">
+        <v>27</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B82" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C82">
+        <v>28</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B83" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C83">
+        <v>29</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B84" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C84">
+        <v>30</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E84"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3415,7 +6235,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E84"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3436,13 +6256,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -3453,13 +6273,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -3470,13 +6290,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -3487,13 +6307,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -3504,13 +6324,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -3521,13 +6341,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B7" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -3538,13 +6358,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B8" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -3555,13 +6375,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B9" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -3572,13 +6392,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B10" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -3589,13 +6409,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B11" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -3606,13 +6426,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B12" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -3623,13 +6443,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B13" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -3640,13 +6460,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B14" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -3657,13 +6477,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B15" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -3674,13 +6494,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B16" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -3691,13 +6511,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B17" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -3708,13 +6528,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B18" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -3725,13 +6545,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B19" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -3742,13 +6562,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B20" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -3759,13 +6579,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B21" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -3776,13 +6596,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B22" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -3793,13 +6613,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B23" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -3810,13 +6630,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B24" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C24">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -3827,13 +6647,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B25" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -3844,13 +6664,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B26" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -3861,13 +6681,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B27" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -3878,13 +6698,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B28" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -3895,13 +6715,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B29" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -3912,13 +6732,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B30" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C30">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -3929,13 +6749,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B31" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -3946,13 +6766,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B32" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -3963,13 +6783,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B33" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C33">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -3980,13 +6800,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B34" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C34">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -3997,13 +6817,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B35" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C35">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -4014,13 +6834,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B36" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -4031,24 +6851,823 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-05</v>
+        <v>2026-04</v>
       </c>
       <c r="B37" t="str">
-        <v>dia</v>
+        <v>semana</v>
       </c>
       <c r="C37">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B38" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C38">
+        <v>37</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B39" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B40" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C40">
+        <v>39</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B41" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B42" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B43" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C43">
+        <v>42</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B44" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B45" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C45">
+        <v>44</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B46" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B47" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C47">
+        <v>46</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B48" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C48">
+        <v>47</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B49" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C49">
+        <v>48</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B50" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C50">
+        <v>49</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B51" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B52" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C52">
+        <v>51</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B53" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C53">
+        <v>52</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B54" t="str">
+        <v>semana</v>
+      </c>
+      <c r="C54">
+        <v>53</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B55" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B56" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B57" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B58" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B59" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B60" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C60">
+        <v>6</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B61" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B62" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B63" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C63">
+        <v>9</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B64" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B65" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C65">
+        <v>11</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B66" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C66">
+        <v>12</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B67" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C67">
+        <v>13</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B68" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C68">
+        <v>14</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B69" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C69">
+        <v>15</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B70" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C70">
+        <v>16</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B71" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C71">
+        <v>17</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B72" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C72">
+        <v>18</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B73" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C73">
+        <v>19</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B74" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C74">
+        <v>20</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B75" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C75">
+        <v>21</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B76" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C76">
+        <v>22</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B77" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C77">
+        <v>23</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B78" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C78">
+        <v>24</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B79" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C79">
+        <v>25</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B80" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C80">
+        <v>26</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B81" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C81">
+        <v>27</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B82" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C82">
+        <v>28</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B83" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C83">
+        <v>29</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-04</v>
+      </c>
+      <c r="B84" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C84">
+        <v>30</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E84"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/assets/plantilla-importacion-indicadores.xlsx
+++ b/assets/plantilla-importacion-indicadores.xlsx
@@ -430,7 +430,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. Esta plantilla se genera con el mes de referencia: año 2026, mes 4 (2026-04).</v>
+        <v>2. Esta plantilla se genera con el mes de referencia: año 2026, mes 5 (2026-05).</v>
       </c>
     </row>
     <row r="6">
@@ -445,7 +445,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>4. En *_detalle: filas semana = semanas ISO 1-53 (como en pantalla Captura); luego filas dia = días 1-30 del mes.</v>
+        <v>4. En *_detalle: filas semana = semanas ISO 1-53 (como en pantalla Captura); luego filas dia = días 1-31 del mes.</v>
       </c>
     </row>
     <row r="9">
@@ -480,7 +480,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>carros_detalle — Semanas ISO 1-53 + un día por fila del mes (1-30), clave_mes 2026-04</v>
+        <v>carros_detalle — Semanas ISO 1-53 + un día por fila del mes (1-31), clave_mes 2026-05</v>
       </c>
     </row>
     <row r="16">
@@ -507,7 +507,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -528,7 +528,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
@@ -545,7 +545,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
@@ -596,7 +596,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
@@ -613,7 +613,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B7" t="str">
         <v>semana</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B8" t="str">
         <v>semana</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B9" t="str">
         <v>semana</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B10" t="str">
         <v>semana</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B11" t="str">
         <v>semana</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B12" t="str">
         <v>semana</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B13" t="str">
         <v>semana</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B14" t="str">
         <v>semana</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B15" t="str">
         <v>semana</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B16" t="str">
         <v>semana</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B17" t="str">
         <v>semana</v>
@@ -800,7 +800,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B18" t="str">
         <v>semana</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B19" t="str">
         <v>semana</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B20" t="str">
         <v>semana</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B21" t="str">
         <v>semana</v>
@@ -868,7 +868,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B22" t="str">
         <v>semana</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B23" t="str">
         <v>semana</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B24" t="str">
         <v>semana</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B25" t="str">
         <v>semana</v>
@@ -936,7 +936,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B26" t="str">
         <v>semana</v>
@@ -953,7 +953,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B27" t="str">
         <v>semana</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B28" t="str">
         <v>semana</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B29" t="str">
         <v>semana</v>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B30" t="str">
         <v>semana</v>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B31" t="str">
         <v>semana</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B32" t="str">
         <v>semana</v>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B33" t="str">
         <v>semana</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B34" t="str">
         <v>semana</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B35" t="str">
         <v>semana</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B36" t="str">
         <v>semana</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B37" t="str">
         <v>semana</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B38" t="str">
         <v>semana</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B39" t="str">
         <v>semana</v>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B40" t="str">
         <v>semana</v>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B41" t="str">
         <v>semana</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B42" t="str">
         <v>semana</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B43" t="str">
         <v>semana</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B44" t="str">
         <v>semana</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B45" t="str">
         <v>semana</v>
@@ -1276,7 +1276,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B46" t="str">
         <v>semana</v>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B47" t="str">
         <v>semana</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B48" t="str">
         <v>semana</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B49" t="str">
         <v>semana</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B50" t="str">
         <v>semana</v>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B51" t="str">
         <v>semana</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B52" t="str">
         <v>semana</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B53" t="str">
         <v>semana</v>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B54" t="str">
         <v>semana</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B55" t="str">
         <v>dia</v>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B56" t="str">
         <v>dia</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B57" t="str">
         <v>dia</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B58" t="str">
         <v>dia</v>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B59" t="str">
         <v>dia</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B60" t="str">
         <v>dia</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B61" t="str">
         <v>dia</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B62" t="str">
         <v>dia</v>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B63" t="str">
         <v>dia</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B64" t="str">
         <v>dia</v>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B65" t="str">
         <v>dia</v>
@@ -1616,7 +1616,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B66" t="str">
         <v>dia</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B67" t="str">
         <v>dia</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B68" t="str">
         <v>dia</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B69" t="str">
         <v>dia</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B70" t="str">
         <v>dia</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B71" t="str">
         <v>dia</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B72" t="str">
         <v>dia</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B73" t="str">
         <v>dia</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B74" t="str">
         <v>dia</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B75" t="str">
         <v>dia</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B76" t="str">
         <v>dia</v>
@@ -1803,7 +1803,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B77" t="str">
         <v>dia</v>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B78" t="str">
         <v>dia</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B79" t="str">
         <v>dia</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B80" t="str">
         <v>dia</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B81" t="str">
         <v>dia</v>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B82" t="str">
         <v>dia</v>
@@ -1905,7 +1905,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B83" t="str">
         <v>dia</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B84" t="str">
         <v>dia</v>
@@ -1937,9 +1937,26 @@
         <v/>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B85" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C85">
+        <v>31</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E84"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2215,7 +2232,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2245,7 +2262,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
@@ -2271,7 +2288,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
@@ -2297,7 +2314,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
@@ -2323,7 +2340,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
@@ -2349,7 +2366,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
@@ -2375,7 +2392,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B7" t="str">
         <v>semana</v>
@@ -2401,7 +2418,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B8" t="str">
         <v>semana</v>
@@ -2427,7 +2444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B9" t="str">
         <v>semana</v>
@@ -2453,7 +2470,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B10" t="str">
         <v>semana</v>
@@ -2479,7 +2496,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B11" t="str">
         <v>semana</v>
@@ -2505,7 +2522,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B12" t="str">
         <v>semana</v>
@@ -2531,7 +2548,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B13" t="str">
         <v>semana</v>
@@ -2557,7 +2574,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B14" t="str">
         <v>semana</v>
@@ -2583,7 +2600,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B15" t="str">
         <v>semana</v>
@@ -2609,7 +2626,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B16" t="str">
         <v>semana</v>
@@ -2635,7 +2652,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B17" t="str">
         <v>semana</v>
@@ -2661,7 +2678,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B18" t="str">
         <v>semana</v>
@@ -2687,7 +2704,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B19" t="str">
         <v>semana</v>
@@ -2713,7 +2730,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B20" t="str">
         <v>semana</v>
@@ -2739,7 +2756,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B21" t="str">
         <v>semana</v>
@@ -2765,7 +2782,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B22" t="str">
         <v>semana</v>
@@ -2791,7 +2808,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B23" t="str">
         <v>semana</v>
@@ -2817,7 +2834,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B24" t="str">
         <v>semana</v>
@@ -2843,7 +2860,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B25" t="str">
         <v>semana</v>
@@ -2869,7 +2886,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B26" t="str">
         <v>semana</v>
@@ -2895,7 +2912,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B27" t="str">
         <v>semana</v>
@@ -2921,7 +2938,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B28" t="str">
         <v>semana</v>
@@ -2947,7 +2964,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B29" t="str">
         <v>semana</v>
@@ -2973,7 +2990,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B30" t="str">
         <v>semana</v>
@@ -2999,7 +3016,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B31" t="str">
         <v>semana</v>
@@ -3025,7 +3042,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B32" t="str">
         <v>semana</v>
@@ -3051,7 +3068,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B33" t="str">
         <v>semana</v>
@@ -3077,7 +3094,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B34" t="str">
         <v>semana</v>
@@ -3103,7 +3120,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B35" t="str">
         <v>semana</v>
@@ -3129,7 +3146,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B36" t="str">
         <v>semana</v>
@@ -3155,7 +3172,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B37" t="str">
         <v>semana</v>
@@ -3181,7 +3198,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B38" t="str">
         <v>semana</v>
@@ -3207,7 +3224,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B39" t="str">
         <v>semana</v>
@@ -3233,7 +3250,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B40" t="str">
         <v>semana</v>
@@ -3259,7 +3276,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B41" t="str">
         <v>semana</v>
@@ -3285,7 +3302,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B42" t="str">
         <v>semana</v>
@@ -3311,7 +3328,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B43" t="str">
         <v>semana</v>
@@ -3337,7 +3354,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B44" t="str">
         <v>semana</v>
@@ -3363,7 +3380,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B45" t="str">
         <v>semana</v>
@@ -3389,7 +3406,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B46" t="str">
         <v>semana</v>
@@ -3415,7 +3432,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B47" t="str">
         <v>semana</v>
@@ -3441,7 +3458,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B48" t="str">
         <v>semana</v>
@@ -3467,7 +3484,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B49" t="str">
         <v>semana</v>
@@ -3493,7 +3510,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B50" t="str">
         <v>semana</v>
@@ -3519,7 +3536,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B51" t="str">
         <v>semana</v>
@@ -3545,7 +3562,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B52" t="str">
         <v>semana</v>
@@ -3571,7 +3588,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B53" t="str">
         <v>semana</v>
@@ -3597,7 +3614,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B54" t="str">
         <v>semana</v>
@@ -3623,7 +3640,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B55" t="str">
         <v>dia</v>
@@ -3649,7 +3666,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B56" t="str">
         <v>dia</v>
@@ -3675,7 +3692,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B57" t="str">
         <v>dia</v>
@@ -3701,7 +3718,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B58" t="str">
         <v>dia</v>
@@ -3727,7 +3744,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B59" t="str">
         <v>dia</v>
@@ -3753,7 +3770,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B60" t="str">
         <v>dia</v>
@@ -3779,7 +3796,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B61" t="str">
         <v>dia</v>
@@ -3805,7 +3822,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B62" t="str">
         <v>dia</v>
@@ -3831,7 +3848,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B63" t="str">
         <v>dia</v>
@@ -3857,7 +3874,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B64" t="str">
         <v>dia</v>
@@ -3883,7 +3900,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B65" t="str">
         <v>dia</v>
@@ -3909,7 +3926,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B66" t="str">
         <v>dia</v>
@@ -3935,7 +3952,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B67" t="str">
         <v>dia</v>
@@ -3961,7 +3978,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B68" t="str">
         <v>dia</v>
@@ -3987,7 +4004,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B69" t="str">
         <v>dia</v>
@@ -4013,7 +4030,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B70" t="str">
         <v>dia</v>
@@ -4039,7 +4056,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B71" t="str">
         <v>dia</v>
@@ -4065,7 +4082,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B72" t="str">
         <v>dia</v>
@@ -4091,7 +4108,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B73" t="str">
         <v>dia</v>
@@ -4117,7 +4134,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B74" t="str">
         <v>dia</v>
@@ -4143,7 +4160,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B75" t="str">
         <v>dia</v>
@@ -4169,7 +4186,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B76" t="str">
         <v>dia</v>
@@ -4195,7 +4212,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B77" t="str">
         <v>dia</v>
@@ -4221,7 +4238,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B78" t="str">
         <v>dia</v>
@@ -4247,7 +4264,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B79" t="str">
         <v>dia</v>
@@ -4273,7 +4290,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B80" t="str">
         <v>dia</v>
@@ -4299,7 +4316,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B81" t="str">
         <v>dia</v>
@@ -4325,7 +4342,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B82" t="str">
         <v>dia</v>
@@ -4351,7 +4368,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B83" t="str">
         <v>dia</v>
@@ -4377,7 +4394,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B84" t="str">
         <v>dia</v>
@@ -4401,9 +4418,35 @@
         <v/>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B85" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C85">
+        <v>31</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H84"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H85"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4603,7 +4646,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4624,7 +4667,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
@@ -4641,7 +4684,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
@@ -4658,7 +4701,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
@@ -4675,7 +4718,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
@@ -4692,7 +4735,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
@@ -4709,7 +4752,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B7" t="str">
         <v>semana</v>
@@ -4726,7 +4769,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B8" t="str">
         <v>semana</v>
@@ -4743,7 +4786,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B9" t="str">
         <v>semana</v>
@@ -4760,7 +4803,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B10" t="str">
         <v>semana</v>
@@ -4777,7 +4820,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B11" t="str">
         <v>semana</v>
@@ -4794,7 +4837,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B12" t="str">
         <v>semana</v>
@@ -4811,7 +4854,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B13" t="str">
         <v>semana</v>
@@ -4828,7 +4871,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B14" t="str">
         <v>semana</v>
@@ -4845,7 +4888,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B15" t="str">
         <v>semana</v>
@@ -4862,7 +4905,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B16" t="str">
         <v>semana</v>
@@ -4879,7 +4922,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B17" t="str">
         <v>semana</v>
@@ -4896,7 +4939,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B18" t="str">
         <v>semana</v>
@@ -4913,7 +4956,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B19" t="str">
         <v>semana</v>
@@ -4930,7 +4973,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B20" t="str">
         <v>semana</v>
@@ -4947,7 +4990,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B21" t="str">
         <v>semana</v>
@@ -4964,7 +5007,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B22" t="str">
         <v>semana</v>
@@ -4981,7 +5024,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B23" t="str">
         <v>semana</v>
@@ -4998,7 +5041,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B24" t="str">
         <v>semana</v>
@@ -5015,7 +5058,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B25" t="str">
         <v>semana</v>
@@ -5032,7 +5075,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B26" t="str">
         <v>semana</v>
@@ -5049,7 +5092,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B27" t="str">
         <v>semana</v>
@@ -5066,7 +5109,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B28" t="str">
         <v>semana</v>
@@ -5083,7 +5126,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B29" t="str">
         <v>semana</v>
@@ -5100,7 +5143,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B30" t="str">
         <v>semana</v>
@@ -5117,7 +5160,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B31" t="str">
         <v>semana</v>
@@ -5134,7 +5177,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B32" t="str">
         <v>semana</v>
@@ -5151,7 +5194,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B33" t="str">
         <v>semana</v>
@@ -5168,7 +5211,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B34" t="str">
         <v>semana</v>
@@ -5185,7 +5228,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B35" t="str">
         <v>semana</v>
@@ -5202,7 +5245,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B36" t="str">
         <v>semana</v>
@@ -5219,7 +5262,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B37" t="str">
         <v>semana</v>
@@ -5236,7 +5279,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B38" t="str">
         <v>semana</v>
@@ -5253,7 +5296,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B39" t="str">
         <v>semana</v>
@@ -5270,7 +5313,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B40" t="str">
         <v>semana</v>
@@ -5287,7 +5330,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B41" t="str">
         <v>semana</v>
@@ -5304,7 +5347,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B42" t="str">
         <v>semana</v>
@@ -5321,7 +5364,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B43" t="str">
         <v>semana</v>
@@ -5338,7 +5381,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B44" t="str">
         <v>semana</v>
@@ -5355,7 +5398,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B45" t="str">
         <v>semana</v>
@@ -5372,7 +5415,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B46" t="str">
         <v>semana</v>
@@ -5389,7 +5432,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B47" t="str">
         <v>semana</v>
@@ -5406,7 +5449,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B48" t="str">
         <v>semana</v>
@@ -5423,7 +5466,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B49" t="str">
         <v>semana</v>
@@ -5440,7 +5483,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B50" t="str">
         <v>semana</v>
@@ -5457,7 +5500,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B51" t="str">
         <v>semana</v>
@@ -5474,7 +5517,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B52" t="str">
         <v>semana</v>
@@ -5491,7 +5534,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B53" t="str">
         <v>semana</v>
@@ -5508,7 +5551,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B54" t="str">
         <v>semana</v>
@@ -5525,7 +5568,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B55" t="str">
         <v>dia</v>
@@ -5542,7 +5585,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B56" t="str">
         <v>dia</v>
@@ -5559,7 +5602,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B57" t="str">
         <v>dia</v>
@@ -5576,7 +5619,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B58" t="str">
         <v>dia</v>
@@ -5593,7 +5636,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B59" t="str">
         <v>dia</v>
@@ -5610,7 +5653,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B60" t="str">
         <v>dia</v>
@@ -5627,7 +5670,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B61" t="str">
         <v>dia</v>
@@ -5644,7 +5687,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B62" t="str">
         <v>dia</v>
@@ -5661,7 +5704,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B63" t="str">
         <v>dia</v>
@@ -5678,7 +5721,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B64" t="str">
         <v>dia</v>
@@ -5695,7 +5738,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B65" t="str">
         <v>dia</v>
@@ -5712,7 +5755,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B66" t="str">
         <v>dia</v>
@@ -5729,7 +5772,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B67" t="str">
         <v>dia</v>
@@ -5746,7 +5789,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B68" t="str">
         <v>dia</v>
@@ -5763,7 +5806,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B69" t="str">
         <v>dia</v>
@@ -5780,7 +5823,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B70" t="str">
         <v>dia</v>
@@ -5797,7 +5840,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B71" t="str">
         <v>dia</v>
@@ -5814,7 +5857,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B72" t="str">
         <v>dia</v>
@@ -5831,7 +5874,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B73" t="str">
         <v>dia</v>
@@ -5848,7 +5891,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B74" t="str">
         <v>dia</v>
@@ -5865,7 +5908,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B75" t="str">
         <v>dia</v>
@@ -5882,7 +5925,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B76" t="str">
         <v>dia</v>
@@ -5899,7 +5942,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B77" t="str">
         <v>dia</v>
@@ -5916,7 +5959,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B78" t="str">
         <v>dia</v>
@@ -5933,7 +5976,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B79" t="str">
         <v>dia</v>
@@ -5950,7 +5993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B80" t="str">
         <v>dia</v>
@@ -5967,7 +6010,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B81" t="str">
         <v>dia</v>
@@ -5984,7 +6027,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B82" t="str">
         <v>dia</v>
@@ -6001,7 +6044,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B83" t="str">
         <v>dia</v>
@@ -6018,7 +6061,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B84" t="str">
         <v>dia</v>
@@ -6033,9 +6076,26 @@
         <v/>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B85" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C85">
+        <v>31</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E84"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6235,7 +6295,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6256,7 +6316,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B2" t="str">
         <v>semana</v>
@@ -6273,7 +6333,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B3" t="str">
         <v>semana</v>
@@ -6290,7 +6350,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B4" t="str">
         <v>semana</v>
@@ -6307,7 +6367,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B5" t="str">
         <v>semana</v>
@@ -6324,7 +6384,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B6" t="str">
         <v>semana</v>
@@ -6341,7 +6401,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B7" t="str">
         <v>semana</v>
@@ -6358,7 +6418,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B8" t="str">
         <v>semana</v>
@@ -6375,7 +6435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B9" t="str">
         <v>semana</v>
@@ -6392,7 +6452,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B10" t="str">
         <v>semana</v>
@@ -6409,7 +6469,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B11" t="str">
         <v>semana</v>
@@ -6426,7 +6486,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B12" t="str">
         <v>semana</v>
@@ -6443,7 +6503,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B13" t="str">
         <v>semana</v>
@@ -6460,7 +6520,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B14" t="str">
         <v>semana</v>
@@ -6477,7 +6537,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B15" t="str">
         <v>semana</v>
@@ -6494,7 +6554,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B16" t="str">
         <v>semana</v>
@@ -6511,7 +6571,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B17" t="str">
         <v>semana</v>
@@ -6528,7 +6588,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B18" t="str">
         <v>semana</v>
@@ -6545,7 +6605,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B19" t="str">
         <v>semana</v>
@@ -6562,7 +6622,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B20" t="str">
         <v>semana</v>
@@ -6579,7 +6639,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B21" t="str">
         <v>semana</v>
@@ -6596,7 +6656,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B22" t="str">
         <v>semana</v>
@@ -6613,7 +6673,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B23" t="str">
         <v>semana</v>
@@ -6630,7 +6690,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B24" t="str">
         <v>semana</v>
@@ -6647,7 +6707,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B25" t="str">
         <v>semana</v>
@@ -6664,7 +6724,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B26" t="str">
         <v>semana</v>
@@ -6681,7 +6741,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B27" t="str">
         <v>semana</v>
@@ -6698,7 +6758,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B28" t="str">
         <v>semana</v>
@@ -6715,7 +6775,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B29" t="str">
         <v>semana</v>
@@ -6732,7 +6792,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B30" t="str">
         <v>semana</v>
@@ -6749,7 +6809,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B31" t="str">
         <v>semana</v>
@@ -6766,7 +6826,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B32" t="str">
         <v>semana</v>
@@ -6783,7 +6843,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B33" t="str">
         <v>semana</v>
@@ -6800,7 +6860,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B34" t="str">
         <v>semana</v>
@@ -6817,7 +6877,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B35" t="str">
         <v>semana</v>
@@ -6834,7 +6894,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B36" t="str">
         <v>semana</v>
@@ -6851,7 +6911,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B37" t="str">
         <v>semana</v>
@@ -6868,7 +6928,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B38" t="str">
         <v>semana</v>
@@ -6885,7 +6945,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B39" t="str">
         <v>semana</v>
@@ -6902,7 +6962,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B40" t="str">
         <v>semana</v>
@@ -6919,7 +6979,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B41" t="str">
         <v>semana</v>
@@ -6936,7 +6996,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B42" t="str">
         <v>semana</v>
@@ -6953,7 +7013,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B43" t="str">
         <v>semana</v>
@@ -6970,7 +7030,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B44" t="str">
         <v>semana</v>
@@ -6987,7 +7047,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B45" t="str">
         <v>semana</v>
@@ -7004,7 +7064,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B46" t="str">
         <v>semana</v>
@@ -7021,7 +7081,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B47" t="str">
         <v>semana</v>
@@ -7038,7 +7098,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B48" t="str">
         <v>semana</v>
@@ -7055,7 +7115,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B49" t="str">
         <v>semana</v>
@@ -7072,7 +7132,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B50" t="str">
         <v>semana</v>
@@ -7089,7 +7149,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B51" t="str">
         <v>semana</v>
@@ -7106,7 +7166,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B52" t="str">
         <v>semana</v>
@@ -7123,7 +7183,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B53" t="str">
         <v>semana</v>
@@ -7140,7 +7200,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B54" t="str">
         <v>semana</v>
@@ -7157,7 +7217,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B55" t="str">
         <v>dia</v>
@@ -7174,7 +7234,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B56" t="str">
         <v>dia</v>
@@ -7191,7 +7251,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B57" t="str">
         <v>dia</v>
@@ -7208,7 +7268,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B58" t="str">
         <v>dia</v>
@@ -7225,7 +7285,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B59" t="str">
         <v>dia</v>
@@ -7242,7 +7302,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B60" t="str">
         <v>dia</v>
@@ -7259,7 +7319,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B61" t="str">
         <v>dia</v>
@@ -7276,7 +7336,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B62" t="str">
         <v>dia</v>
@@ -7293,7 +7353,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B63" t="str">
         <v>dia</v>
@@ -7310,7 +7370,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B64" t="str">
         <v>dia</v>
@@ -7327,7 +7387,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B65" t="str">
         <v>dia</v>
@@ -7344,7 +7404,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B66" t="str">
         <v>dia</v>
@@ -7361,7 +7421,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B67" t="str">
         <v>dia</v>
@@ -7378,7 +7438,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B68" t="str">
         <v>dia</v>
@@ -7395,7 +7455,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B69" t="str">
         <v>dia</v>
@@ -7412,7 +7472,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B70" t="str">
         <v>dia</v>
@@ -7429,7 +7489,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B71" t="str">
         <v>dia</v>
@@ -7446,7 +7506,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B72" t="str">
         <v>dia</v>
@@ -7463,7 +7523,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B73" t="str">
         <v>dia</v>
@@ -7480,7 +7540,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B74" t="str">
         <v>dia</v>
@@ -7497,7 +7557,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B75" t="str">
         <v>dia</v>
@@ -7514,7 +7574,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B76" t="str">
         <v>dia</v>
@@ -7531,7 +7591,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B77" t="str">
         <v>dia</v>
@@ -7548,7 +7608,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B78" t="str">
         <v>dia</v>
@@ -7565,7 +7625,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B79" t="str">
         <v>dia</v>
@@ -7582,7 +7642,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B80" t="str">
         <v>dia</v>
@@ -7599,7 +7659,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B81" t="str">
         <v>dia</v>
@@ -7616,7 +7676,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B82" t="str">
         <v>dia</v>
@@ -7633,7 +7693,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B83" t="str">
         <v>dia</v>
@@ -7650,7 +7710,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026-04</v>
+        <v>2026-05</v>
       </c>
       <c r="B84" t="str">
         <v>dia</v>
@@ -7665,9 +7725,26 @@
         <v/>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-05</v>
+      </c>
+      <c r="B85" t="str">
+        <v>dia</v>
+      </c>
+      <c r="C85">
+        <v>31</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E84"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E85"/>
   </ignoredErrors>
 </worksheet>
 </file>
